--- a/data/backgrounds.xlsx
+++ b/data/backgrounds.xlsx
@@ -1,46 +1,128 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\StarWrought\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E190F04-6B87-47A2-A852-858F236151D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4935" yWindow="4935" windowWidth="36450" windowHeight="13980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Backgrounds" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Backgrounds" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Effect (format text in this cell: bold/italic/color mirror into the game)</t>
+  </si>
+  <si>
+    <t>Skills (Training in BOTH; 1 TP each)</t>
+  </si>
+  <si>
+    <t>Lore (1 Lore TP)</t>
+  </si>
+  <si>
+    <t>Acrobat</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>In a circus or on the streets, you earned your pay by performing as an acrobat. You might have turned to adventuring when the money dried up, or simply decided to put your skills to better use.</t>
+  </si>
+  <si>
+    <t>You become Trained in Athletics and in Acrobatics, and you become Trained in Lore (Circus).</t>
+  </si>
+  <si>
+    <t>Athletics, Acrobatics</t>
+  </si>
+  <si>
+    <t>Lore (Circus)</t>
+  </si>
+  <si>
+    <t>Soldier</t>
+  </si>
+  <si>
+    <t>You served in somebody's army: a levy, a free company, a city watch that saw real fighting. You learned the drill, the marching, and the waiting, and you learned what a line looks like just before it breaks.</t>
+  </si>
+  <si>
+    <t>You become Trained in Athletics and in Intimidation, and you become Trained in Lore (Warfare).</t>
+  </si>
+  <si>
+    <t>Athletics, Intimidation</t>
+  </si>
+  <si>
+    <t>Lore (Warfare)</t>
+  </si>
+  <si>
+    <t>Criminal</t>
+  </si>
+  <si>
+    <t>You made your living outside the law, whether by picking pockets, running contraband, or talking your way through doors that were meant to stay shut. You still know who to ask, and which questions never to.</t>
+  </si>
+  <si>
+    <t>You become Trained in Guile and in Stealth, and you become Trained in Lore (Underworld).</t>
+  </si>
+  <si>
+    <t>Guile, Stealth</t>
+  </si>
+  <si>
+    <t>Lore (Underworld)</t>
+  </si>
+  <si>
+    <t>Enabled?</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E5F6B"/>
+        <fgColor rgb="FF0E5F6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,86 +139,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,148 +447,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="88" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Background</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Rarity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Effect (format text in this cell: bold/italic/color mirror into the game)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Skills (Training in BOTH; 1 TP each)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Lore (1 Lore TP)</t>
-        </is>
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Acrobat</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>In a circus or on the streets, you earned your pay by performing as an acrobat. You might have turned to adventuring when the money dried up, or simply decided to put your skills to better use.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>You become Trained in Athletics and in Acrobatics, and you become Trained in Lore (Circus).</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Athletics, Acrobatics</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Lore (Circus)</t>
-        </is>
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Soldier</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>You served in somebody's army: a levy, a free company, a city watch that saw real fighting. You learned the drill, the marching, and the waiting, and you learned what a line looks like just before it breaks.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>You become Trained in Athletics and in Intimidation, and you become Trained in Lore (Warfare).</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Athletics, Intimidation</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Lore (Warfare)</t>
-        </is>
-      </c>
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Criminal</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>You made your living outside the law, whether by picking pockets, running contraband, or talking your way through doors that were meant to stay shut. You still know who to ask, and which questions never to.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>You become Trained in Guile and in Stealth, and you become Trained in Lore (Underworld).</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Guile, Stealth</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Lore (Underworld)</t>
-        </is>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
